--- a/vse-loti/339444665/spec-339444665.xlsx
+++ b/vse-loti/339444665/spec-339444665.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +61,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,14 +441,14 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,7 +512,7 @@
           <t>ТРУБА 108Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -513,22 +520,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="F2" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G2" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="F2" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H2" s="3" t="n">
         <v>27147.54</v>
       </c>
-      <c r="I2" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="I2" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -541,7 +548,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -549,22 +556,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="E3" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H3" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="I3" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -577,7 +584,7 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -585,22 +592,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G4" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="E4" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I4" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="I4" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -613,7 +620,7 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -621,22 +628,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G5" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="E5" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I5" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="I5" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -649,7 +656,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -657,22 +664,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G6" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="E6" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I6" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="I6" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -685,7 +692,7 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -693,22 +700,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G7" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="E7" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I7" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="I7" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -721,7 +728,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -729,22 +736,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G8" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="E8" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H8" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I8" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="I8" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J8" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -757,7 +764,7 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -765,22 +772,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G9" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="E9" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I9" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="I9" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J9" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -793,7 +800,7 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -801,22 +808,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F10" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G10" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="E10" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H10" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I10" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="I10" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J10" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -829,7 +836,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -837,22 +844,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G11" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="E11" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I11" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="I11" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J11" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -865,7 +872,7 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -873,22 +880,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G12" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="E12" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I12" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="I12" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J12" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -901,7 +908,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -909,22 +916,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F13" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G13" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="F13" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H13" s="3" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I13" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="I13" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J13" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -937,7 +944,7 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="2" t="n">
         <v>1.5</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -945,22 +952,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F14" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G14" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="F14" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H14" s="3" t="n">
         <v>101803.28</v>
       </c>
-      <c r="I14" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="I14" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J14" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -973,7 +980,7 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -981,22 +988,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="F15" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G15" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="F15" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H15" s="3" t="n">
         <v>13573.77</v>
       </c>
-      <c r="I15" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="I15" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J15" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1009,7 +1016,7 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -1017,22 +1024,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F16" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G16" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H16" t="n">
+      <c r="F16" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H16" s="3" t="n">
         <v>6786.89</v>
       </c>
-      <c r="I16" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="I16" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1045,7 +1052,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -1053,22 +1060,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F17" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G17" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="F17" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H17" s="3" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I17" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="I17" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J17" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1081,7 +1088,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -1089,22 +1096,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G18" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H18" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="E18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J18" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1117,7 +1124,7 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -1125,22 +1132,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G19" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H19" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1153,7 +1160,7 @@
           <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -1161,22 +1168,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="3" t="n">
         <v>83803.28</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="3" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -1189,7 +1196,7 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -1197,22 +1204,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F21" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G21" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="E21" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H21" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I21" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="I21" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J21" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1225,7 +1232,7 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -1233,22 +1240,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F22" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G22" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="E22" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I22" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="I22" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J22" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1261,7 +1268,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -1269,22 +1276,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F23" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G23" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="E23" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H23" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I23" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="I23" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J23" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1297,7 +1304,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -1305,22 +1312,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G24" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H24" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J24" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1333,7 +1340,7 @@
           <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -1341,22 +1348,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="F25" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G25" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="F25" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H25" s="3" t="n">
         <v>54295.08</v>
       </c>
-      <c r="I25" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="I25" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J25" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1369,7 +1376,7 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -1377,22 +1384,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G26" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H26" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="E26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J26" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1405,7 +1412,7 @@
           <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -1413,22 +1420,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" s="3" t="n">
         <v>83803.28</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="3" t="n">
         <v>34918.03</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="3" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -1441,7 +1448,7 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -1449,22 +1456,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F28" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G28" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="E28" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I28" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="I28" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J28" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1477,7 +1484,7 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -1485,22 +1492,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F29" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G29" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H29" t="n">
+      <c r="F29" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H29" s="3" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I29" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="I29" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J29" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1513,7 +1520,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -1521,22 +1528,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F30" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G30" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H30" t="n">
+      <c r="E30" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H30" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I30" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="I30" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J30" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1549,7 +1556,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -1557,22 +1564,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="F31" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G31" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H31" t="n">
+      <c r="F31" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H31" s="3" t="n">
         <v>10180.33</v>
       </c>
-      <c r="I31" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J31" t="n">
+      <c r="I31" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1585,7 +1592,7 @@
           <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="2" t="n">
         <v>0.25</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -1593,22 +1600,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="F32" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G32" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H32" t="n">
+      <c r="F32" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H32" s="3" t="n">
         <v>16967.21</v>
       </c>
-      <c r="I32" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="I32" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J32" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1621,7 +1628,7 @@
           <t>ТРУБА 57Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -1629,22 +1636,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="F33" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G33" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H33" t="n">
+      <c r="F33" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>13573.77</v>
       </c>
-      <c r="I33" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="I33" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J33" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1657,7 +1664,7 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -1665,22 +1672,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="F34" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G34" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H34" t="n">
+      <c r="F34" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>13573.77</v>
       </c>
-      <c r="I34" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="I34" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J34" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1693,7 +1700,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -1701,22 +1708,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="F35" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G35" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H35" t="n">
+      <c r="F35" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H35" s="3" t="n">
         <v>13573.77</v>
       </c>
-      <c r="I35" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="I35" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J35" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1729,7 +1736,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -1737,22 +1744,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G36" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H36" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="E36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J36" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1765,7 +1772,7 @@
           <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -1773,22 +1780,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F37" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G37" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H37" t="n">
+      <c r="F37" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H37" s="3" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I37" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J37" t="n">
+      <c r="I37" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J37" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1801,7 +1808,7 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -1809,22 +1816,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G38" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H38" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J38" t="n">
+      <c r="E38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J38" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1837,7 +1844,7 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -1845,22 +1852,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F39" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G39" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H39" t="n">
+      <c r="E39" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I39" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J39" t="n">
+      <c r="I39" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J39" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1873,7 +1880,7 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -1881,22 +1888,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F40" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G40" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H40" t="n">
+      <c r="F40" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I40" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J40" t="n">
+      <c r="I40" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J40" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1909,7 +1916,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -1917,22 +1924,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G41" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H41" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I41" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J41" t="n">
+      <c r="E41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J41" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1945,7 +1952,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -1953,22 +1960,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G42" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H42" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I42" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J42" t="n">
+      <c r="E42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J42" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1981,7 +1988,7 @@
           <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -1989,22 +1996,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
+      <c r="E43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" s="3" t="n">
         <v>83803.28</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" s="3" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -2017,7 +2024,7 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -2025,22 +2032,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E44" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F44" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G44" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H44" t="n">
+      <c r="E44" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I44" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J44" t="n">
+      <c r="I44" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J44" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2053,7 +2060,7 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -2061,22 +2068,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F45" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G45" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H45" t="n">
+      <c r="F45" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H45" s="3" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I45" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J45" t="n">
+      <c r="I45" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J45" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2089,7 +2096,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -2097,22 +2104,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G46" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H46" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I46" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J46" t="n">
+      <c r="E46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J46" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2125,7 +2132,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="2" t="n">
         <v>1.5</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -2133,22 +2140,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F47" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G47" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H47" t="n">
+      <c r="F47" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H47" s="3" t="n">
         <v>101803.28</v>
       </c>
-      <c r="I47" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J47" t="n">
+      <c r="I47" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J47" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2161,7 +2168,7 @@
           <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -2169,22 +2176,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G48" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H48" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I48" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J48" t="n">
+      <c r="E48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J48" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2197,7 +2204,7 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -2205,22 +2212,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G49" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H49" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J49" t="n">
+      <c r="E49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J49" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2233,7 +2240,7 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -2241,22 +2248,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F50" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G50" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H50" t="n">
+      <c r="F50" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H50" s="3" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I50" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J50" t="n">
+      <c r="I50" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J50" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2269,7 +2276,7 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -2277,22 +2284,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F51" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G51" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H51" t="n">
+      <c r="F51" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H51" s="3" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I51" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J51" t="n">
+      <c r="I51" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J51" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2305,7 +2312,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -2313,22 +2320,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G52" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H52" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I52" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J52" t="n">
+      <c r="E52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J52" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2341,7 +2348,7 @@
           <t>ТРУБА 325Х8 17Г1СУ ГОСТ10705</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -2349,22 +2356,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" t="n">
+      <c r="E53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3" t="n">
         <v>75737.7</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53" s="3" t="n">
         <v>90885.25</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="3" t="n">
         <v>75737.7</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53" s="3" t="n">
         <v>75737.7</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" s="3" t="n">
         <v>90885.25</v>
       </c>
     </row>
@@ -2377,7 +2384,7 @@
           <t>ТРУБА 273Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -2385,22 +2392,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E54" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" t="n">
+      <c r="E54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54" s="3" t="n">
         <v>83803.28</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J54" s="3" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -2413,7 +2420,7 @@
           <t>ТРУБА 530Х9 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -2421,22 +2428,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" s="3" t="n">
         <v>88524.59</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55" s="3" t="n">
         <v>106229.51</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="3" t="n">
         <v>44262.3</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55" s="3" t="n">
         <v>88524.59</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J55" s="3" t="n">
         <v>106229.51</v>
       </c>
     </row>
@@ -2449,7 +2456,7 @@
           <t>ТРУБА 630Х9 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -2457,22 +2464,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="3" t="n">
         <v>93442.62</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56" s="3" t="n">
         <v>112131.15</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56" s="3" t="n">
         <v>56065.57</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I56" s="3" t="n">
         <v>93442.62</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J56" s="3" t="n">
         <v>112131.15</v>
       </c>
     </row>
@@ -2485,7 +2492,7 @@
           <t>ТРУБА 325Х8 17Г1СУ ГОСТ10705</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="2" t="n">
         <v>1.5</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -2493,22 +2500,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="3" t="n">
         <v>75737.7</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57" s="3" t="n">
         <v>90885.25</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H57" s="3" t="n">
         <v>113606.56</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I57" s="3" t="n">
         <v>75737.7</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J57" s="3" t="n">
         <v>90885.25</v>
       </c>
     </row>
@@ -2521,7 +2528,7 @@
           <t>ТРУБА 530Х9 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -2529,22 +2536,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="3" t="n">
         <v>88524.59</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58" s="3" t="n">
         <v>106229.51</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" s="3" t="n">
         <v>177049.18</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I58" s="3" t="n">
         <v>88524.59</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J58" s="3" t="n">
         <v>106229.51</v>
       </c>
     </row>
@@ -2557,7 +2564,7 @@
           <t>ТРУБА 630Х9 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="2" t="n">
         <v>1.92</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -2565,22 +2572,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="3" t="n">
         <v>93442.62</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59" s="3" t="n">
         <v>112131.15</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" s="3" t="n">
         <v>179409.84</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59" s="3" t="n">
         <v>93442.62</v>
       </c>
-      <c r="J59" t="n">
+      <c r="J59" s="3" t="n">
         <v>112131.15</v>
       </c>
     </row>
@@ -2593,7 +2600,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -2601,22 +2608,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="F60" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G60" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H60" t="n">
+      <c r="F60" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H60" s="3" t="n">
         <v>13573.77</v>
       </c>
-      <c r="I60" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J60" t="n">
+      <c r="I60" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J60" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2629,7 +2636,7 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -2637,22 +2644,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="F61" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G61" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H61" t="n">
+      <c r="F61" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H61" s="3" t="n">
         <v>10180.33</v>
       </c>
-      <c r="I61" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J61" t="n">
+      <c r="I61" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J61" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2665,7 +2672,7 @@
           <t>ТРУБА 219Х6 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -2673,22 +2680,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62" s="3" t="n">
         <v>83803.28</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62" s="3" t="n">
         <v>6983.61</v>
       </c>
-      <c r="I62" t="n">
+      <c r="I62" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="J62" t="n">
+      <c r="J62" s="3" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -2701,7 +2708,7 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -2709,22 +2716,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F63" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G63" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H63" t="n">
+      <c r="F63" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H63" s="3" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I63" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J63" t="n">
+      <c r="I63" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J63" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2737,7 +2744,7 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -2745,22 +2752,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="F64" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G64" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H64" t="n">
+      <c r="F64" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H64" s="3" t="n">
         <v>10180.33</v>
       </c>
-      <c r="I64" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J64" t="n">
+      <c r="I64" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J64" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2773,7 +2780,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -2781,22 +2788,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="F65" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G65" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H65" t="n">
+      <c r="F65" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H65" s="3" t="n">
         <v>10180.33</v>
       </c>
-      <c r="I65" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J65" t="n">
+      <c r="I65" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J65" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2809,7 +2816,7 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -2817,22 +2824,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="F66" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G66" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H66" t="n">
+      <c r="F66" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H66" s="3" t="n">
         <v>13573.77</v>
       </c>
-      <c r="I66" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J66" t="n">
+      <c r="I66" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J66" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2845,7 +2852,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -2853,22 +2860,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F67" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G67" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H67" t="n">
+      <c r="F67" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H67" s="3" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I67" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J67" t="n">
+      <c r="I67" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J67" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2881,7 +2888,7 @@
           <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -2889,22 +2896,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F68" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G68" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H68" t="n">
+      <c r="F68" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H68" s="3" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I68" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J68" t="n">
+      <c r="I68" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J68" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2917,7 +2924,7 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="2" t="n">
         <v>0.7</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -2925,22 +2932,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="2" t="n">
         <v>0.7</v>
       </c>
-      <c r="F69" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G69" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H69" t="n">
+      <c r="F69" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H69" s="3" t="n">
         <v>47508.2</v>
       </c>
-      <c r="I69" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J69" t="n">
+      <c r="I69" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J69" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2953,7 +2960,7 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -2961,22 +2968,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F70" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G70" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H70" t="n">
+      <c r="E70" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H70" s="3" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I70" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J70" t="n">
+      <c r="I70" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J70" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2989,7 +2996,7 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -2997,22 +3004,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F71" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G71" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H71" t="n">
+      <c r="F71" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H71" s="3" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I71" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J71" t="n">
+      <c r="I71" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J71" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -3025,7 +3032,7 @@
           <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -3033,22 +3040,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72" s="3" t="n">
         <v>83803.28</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H72" s="3" t="n">
         <v>41901.64</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J72" s="3" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -3061,7 +3068,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -3069,22 +3076,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="F73" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G73" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H73" t="n">
+      <c r="F73" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>81442.62</v>
+      </c>
+      <c r="H73" s="3" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I73" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J73" t="n">
+      <c r="I73" s="3" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="J73" s="3" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -3097,7 +3104,7 @@
           <t>ТРУБА 273Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -3105,22 +3112,22 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G74" s="3" t="n">
         <v>83803.28</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H74" s="3" t="n">
         <v>27934.43</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I74" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J74" s="3" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -3133,7 +3140,7 @@
           <t>ТРУБА 219Х6 СТ20 ТИП1 К52 ГОСТ20295</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -3141,35 +3148,35 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F75" t="n">
+      <c r="E75" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F75" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G75" s="3" t="n">
         <v>83803.28</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H75" s="3" t="n">
         <v>20950.82</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I75" s="3" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="J75" t="n">
+      <c r="J75" s="3" t="n">
         <v>83803.28</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E76" s="5" t="n">
         <v>43.37</v>
       </c>
-      <c r="H76" s="2" t="n">
+      <c r="H76" s="6" t="n">
         <v>3088868.98</v>
       </c>
     </row>

--- a/vse-loti/339444665/spec-339444665.xlsx
+++ b/vse-loti/339444665/spec-339444665.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.####"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -61,16 +62,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -447,8 +450,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +480,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -520,22 +511,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>27147.54</v>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J2" s="3" t="n">
+      <c r="G2" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H2" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -556,22 +541,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H3" s="3" t="n">
+      <c r="E3" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J3" s="3" t="n">
+      <c r="G3" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H3" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -592,22 +571,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H4" s="3" t="n">
+      <c r="E4" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J4" s="3" t="n">
+      <c r="G4" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H4" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -628,22 +601,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H5" s="3" t="n">
+      <c r="E5" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J5" s="3" t="n">
+      <c r="G5" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -664,22 +631,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H6" s="3" t="n">
+      <c r="E6" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J6" s="3" t="n">
+      <c r="G6" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H6" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -700,22 +661,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H7" s="3" t="n">
+      <c r="E7" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J7" s="3" t="n">
+      <c r="G7" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H7" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -736,22 +691,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H8" s="3" t="n">
+      <c r="E8" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I8" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J8" s="3" t="n">
+      <c r="G8" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H8" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -772,22 +721,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H9" s="3" t="n">
+      <c r="E9" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I9" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J9" s="3" t="n">
+      <c r="G9" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H9" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -808,22 +751,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H10" s="3" t="n">
+      <c r="E10" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I10" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J10" s="3" t="n">
+      <c r="G10" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -844,22 +781,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H11" s="3" t="n">
+      <c r="E11" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J11" s="3" t="n">
+      <c r="G11" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H11" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -880,22 +811,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H12" s="3" t="n">
+      <c r="E12" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J12" s="3" t="n">
+      <c r="G12" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H12" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -916,22 +841,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H13" s="3" t="n">
+      <c r="E13" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I13" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J13" s="3" t="n">
+      <c r="G13" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -952,22 +871,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H14" s="3" t="n">
+      <c r="F14" s="4" t="n">
         <v>101803.28</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J14" s="3" t="n">
+      <c r="G14" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -988,22 +901,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H15" s="3" t="n">
+      <c r="F15" s="4" t="n">
         <v>13573.77</v>
       </c>
-      <c r="I15" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J15" s="3" t="n">
+      <c r="G15" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1024,22 +931,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H16" s="3" t="n">
+      <c r="F16" s="4" t="n">
         <v>6786.89</v>
       </c>
-      <c r="I16" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J16" s="3" t="n">
+      <c r="G16" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H16" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1060,22 +961,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H17" s="3" t="n">
+      <c r="E17" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J17" s="3" t="n">
+      <c r="G17" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H17" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1088,7 +983,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -1096,22 +991,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J18" s="3" t="n">
+      <c r="E18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H18" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1124,7 +1013,7 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -1132,22 +1021,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J19" s="3" t="n">
+      <c r="E19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H19" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1160,7 +1043,7 @@
           <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -1168,22 +1051,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3" t="n">
+      <c r="E20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>83803.28</v>
-      </c>
-      <c r="H20" s="3" t="n">
+      <c r="G20" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>69836.07000000001</v>
-      </c>
-      <c r="J20" s="3" t="n">
+      <c r="H20" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -1204,22 +1081,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H21" s="3" t="n">
+      <c r="E21" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F21" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I21" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J21" s="3" t="n">
+      <c r="G21" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H21" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1240,22 +1111,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H22" s="3" t="n">
+      <c r="E22" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I22" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J22" s="3" t="n">
+      <c r="G22" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H22" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1276,22 +1141,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H23" s="3" t="n">
+      <c r="E23" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F23" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I23" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J23" s="3" t="n">
+      <c r="G23" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H23" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1304,7 +1163,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -1312,22 +1171,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J24" s="3" t="n">
+      <c r="E24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H24" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1348,22 +1201,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H25" s="3" t="n">
+      <c r="F25" s="4" t="n">
         <v>54295.08</v>
       </c>
-      <c r="I25" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J25" s="3" t="n">
+      <c r="G25" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H25" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1376,7 +1223,7 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -1384,22 +1231,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J26" s="3" t="n">
+      <c r="E26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H26" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1420,22 +1261,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F27" s="3" t="n">
+      <c r="E27" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>34918.03</v>
+      </c>
+      <c r="G27" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>83803.28</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>34918.03</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>69836.07000000001</v>
-      </c>
-      <c r="J27" s="3" t="n">
+      <c r="H27" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -1456,22 +1291,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H28" s="3" t="n">
+      <c r="E28" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F28" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I28" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J28" s="3" t="n">
+      <c r="G28" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H28" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1492,22 +1321,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H29" s="3" t="n">
+      <c r="E29" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F29" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I29" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J29" s="3" t="n">
+      <c r="G29" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H29" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1528,22 +1351,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H30" s="3" t="n">
+      <c r="E30" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F30" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I30" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J30" s="3" t="n">
+      <c r="G30" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H30" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1564,22 +1381,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H31" s="3" t="n">
+      <c r="F31" s="4" t="n">
         <v>10180.33</v>
       </c>
-      <c r="I31" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J31" s="3" t="n">
+      <c r="G31" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H31" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1600,22 +1411,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H32" s="3" t="n">
+      <c r="F32" s="4" t="n">
         <v>16967.21</v>
       </c>
-      <c r="I32" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J32" s="3" t="n">
+      <c r="G32" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H32" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1636,22 +1441,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H33" s="3" t="n">
+      <c r="F33" s="4" t="n">
         <v>13573.77</v>
       </c>
-      <c r="I33" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J33" s="3" t="n">
+      <c r="G33" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H33" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1672,22 +1471,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H34" s="3" t="n">
+      <c r="F34" s="4" t="n">
         <v>13573.77</v>
       </c>
-      <c r="I34" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J34" s="3" t="n">
+      <c r="G34" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H34" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1708,22 +1501,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H35" s="3" t="n">
+      <c r="F35" s="4" t="n">
         <v>13573.77</v>
       </c>
-      <c r="I35" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J35" s="3" t="n">
+      <c r="G35" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H35" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1736,7 +1523,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -1744,22 +1531,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J36" s="3" t="n">
+      <c r="E36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H36" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1780,22 +1561,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H37" s="3" t="n">
+      <c r="E37" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F37" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I37" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J37" s="3" t="n">
+      <c r="G37" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H37" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1808,7 +1583,7 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C38" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -1816,22 +1591,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J38" s="3" t="n">
+      <c r="E38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H38" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1852,22 +1621,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H39" s="3" t="n">
+      <c r="E39" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F39" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J39" s="3" t="n">
+      <c r="G39" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H39" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1888,22 +1651,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H40" s="3" t="n">
+      <c r="E40" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F40" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I40" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J40" s="3" t="n">
+      <c r="G40" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H40" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1916,7 +1673,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="C41" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -1924,22 +1681,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J41" s="3" t="n">
+      <c r="E41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H41" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1952,7 +1703,7 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C42" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -1960,22 +1711,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J42" s="3" t="n">
+      <c r="E42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H42" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1988,7 +1733,7 @@
           <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C43" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -1996,22 +1741,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="3" t="n">
+      <c r="E43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>83803.28</v>
-      </c>
-      <c r="H43" s="3" t="n">
+      <c r="G43" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="I43" s="3" t="n">
-        <v>69836.07000000001</v>
-      </c>
-      <c r="J43" s="3" t="n">
+      <c r="H43" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -2032,22 +1771,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H44" s="3" t="n">
+      <c r="E44" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F44" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J44" s="3" t="n">
+      <c r="G44" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H44" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2068,22 +1801,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H45" s="3" t="n">
+      <c r="E45" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F45" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I45" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J45" s="3" t="n">
+      <c r="G45" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H45" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2096,7 +1823,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -2104,22 +1831,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J46" s="3" t="n">
+      <c r="E46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H46" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2140,22 +1861,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E47" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H47" s="3" t="n">
+      <c r="F47" s="4" t="n">
         <v>101803.28</v>
       </c>
-      <c r="I47" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J47" s="3" t="n">
+      <c r="G47" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H47" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2168,7 +1883,7 @@
           <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -2176,22 +1891,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J48" s="3" t="n">
+      <c r="E48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H48" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2204,7 +1913,7 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C49" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -2212,22 +1921,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J49" s="3" t="n">
+      <c r="E49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H49" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2248,22 +1951,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H50" s="3" t="n">
+      <c r="E50" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F50" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I50" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J50" s="3" t="n">
+      <c r="G50" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H50" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2284,22 +1981,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E51" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H51" s="3" t="n">
+      <c r="E51" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F51" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I51" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J51" s="3" t="n">
+      <c r="G51" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H51" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2312,7 +2003,7 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C52" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -2320,22 +2011,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H52" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="I52" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J52" s="3" t="n">
+      <c r="E52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H52" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2348,7 +2033,7 @@
           <t>ТРУБА 325Х8 17Г1СУ ГОСТ10705</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
+      <c r="C53" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -2356,22 +2041,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="3" t="n">
+      <c r="E53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="4" t="n">
         <v>75737.7</v>
       </c>
-      <c r="G53" s="3" t="n">
-        <v>90885.25</v>
-      </c>
-      <c r="H53" s="3" t="n">
+      <c r="G53" s="4" t="n">
         <v>75737.7</v>
       </c>
-      <c r="I53" s="3" t="n">
-        <v>75737.7</v>
-      </c>
-      <c r="J53" s="3" t="n">
+      <c r="H53" s="4" t="n">
         <v>90885.25</v>
       </c>
     </row>
@@ -2384,7 +2063,7 @@
           <t>ТРУБА 273Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
+      <c r="C54" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -2392,22 +2071,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="3" t="n">
+      <c r="E54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G54" s="3" t="n">
-        <v>83803.28</v>
-      </c>
-      <c r="H54" s="3" t="n">
+      <c r="G54" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="I54" s="3" t="n">
-        <v>69836.07000000001</v>
-      </c>
-      <c r="J54" s="3" t="n">
+      <c r="H54" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -2428,22 +2101,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F55" s="3" t="n">
+      <c r="E55" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>44262.3</v>
+      </c>
+      <c r="G55" s="4" t="n">
         <v>88524.59</v>
       </c>
-      <c r="G55" s="3" t="n">
-        <v>106229.51</v>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>44262.3</v>
-      </c>
-      <c r="I55" s="3" t="n">
-        <v>88524.59</v>
-      </c>
-      <c r="J55" s="3" t="n">
+      <c r="H55" s="4" t="n">
         <v>106229.51</v>
       </c>
     </row>
@@ -2464,22 +2131,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="F56" s="3" t="n">
+      <c r="F56" s="4" t="n">
+        <v>56065.57</v>
+      </c>
+      <c r="G56" s="4" t="n">
         <v>93442.62</v>
       </c>
-      <c r="G56" s="3" t="n">
-        <v>112131.15</v>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>56065.57</v>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>93442.62</v>
-      </c>
-      <c r="J56" s="3" t="n">
+      <c r="H56" s="4" t="n">
         <v>112131.15</v>
       </c>
     </row>
@@ -2500,22 +2161,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="E57" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="F57" s="3" t="n">
+      <c r="F57" s="4" t="n">
+        <v>113606.56</v>
+      </c>
+      <c r="G57" s="4" t="n">
         <v>75737.7</v>
       </c>
-      <c r="G57" s="3" t="n">
-        <v>90885.25</v>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>113606.56</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>75737.7</v>
-      </c>
-      <c r="J57" s="3" t="n">
+      <c r="H57" s="4" t="n">
         <v>90885.25</v>
       </c>
     </row>
@@ -2528,7 +2183,7 @@
           <t>ТРУБА 530Х9 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C58" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -2536,22 +2191,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="E58" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="3" t="n">
+      <c r="F58" s="4" t="n">
+        <v>177049.18</v>
+      </c>
+      <c r="G58" s="4" t="n">
         <v>88524.59</v>
       </c>
-      <c r="G58" s="3" t="n">
-        <v>106229.51</v>
-      </c>
-      <c r="H58" s="3" t="n">
-        <v>177049.18</v>
-      </c>
-      <c r="I58" s="3" t="n">
-        <v>88524.59</v>
-      </c>
-      <c r="J58" s="3" t="n">
+      <c r="H58" s="4" t="n">
         <v>106229.51</v>
       </c>
     </row>
@@ -2572,22 +2221,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E59" s="3" t="n">
         <v>1.92</v>
       </c>
-      <c r="F59" s="3" t="n">
+      <c r="F59" s="4" t="n">
+        <v>179409.84</v>
+      </c>
+      <c r="G59" s="4" t="n">
         <v>93442.62</v>
       </c>
-      <c r="G59" s="3" t="n">
-        <v>112131.15</v>
-      </c>
-      <c r="H59" s="3" t="n">
-        <v>179409.84</v>
-      </c>
-      <c r="I59" s="3" t="n">
-        <v>93442.62</v>
-      </c>
-      <c r="J59" s="3" t="n">
+      <c r="H59" s="4" t="n">
         <v>112131.15</v>
       </c>
     </row>
@@ -2608,22 +2251,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="E60" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F60" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H60" s="3" t="n">
+      <c r="F60" s="4" t="n">
         <v>13573.77</v>
       </c>
-      <c r="I60" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J60" s="3" t="n">
+      <c r="G60" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H60" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2644,22 +2281,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="E61" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="F61" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H61" s="3" t="n">
+      <c r="F61" s="4" t="n">
         <v>10180.33</v>
       </c>
-      <c r="I61" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J61" s="3" t="n">
+      <c r="G61" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H61" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2680,22 +2311,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F62" s="3" t="n">
+      <c r="F62" s="4" t="n">
+        <v>6983.61</v>
+      </c>
+      <c r="G62" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G62" s="3" t="n">
-        <v>83803.28</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>6983.61</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>69836.07000000001</v>
-      </c>
-      <c r="J62" s="3" t="n">
+      <c r="H62" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -2716,22 +2341,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E63" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H63" s="3" t="n">
+      <c r="E63" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F63" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I63" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J63" s="3" t="n">
+      <c r="G63" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H63" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2752,22 +2371,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="F64" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H64" s="3" t="n">
+      <c r="F64" s="4" t="n">
         <v>10180.33</v>
       </c>
-      <c r="I64" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J64" s="3" t="n">
+      <c r="G64" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H64" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2788,22 +2401,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E65" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="F65" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H65" s="3" t="n">
+      <c r="F65" s="4" t="n">
         <v>10180.33</v>
       </c>
-      <c r="I65" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J65" s="3" t="n">
+      <c r="G65" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H65" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2824,22 +2431,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E66" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F66" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H66" s="3" t="n">
+      <c r="F66" s="4" t="n">
         <v>13573.77</v>
       </c>
-      <c r="I66" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J66" s="3" t="n">
+      <c r="G66" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H66" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2860,22 +2461,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E67" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H67" s="3" t="n">
+      <c r="E67" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F67" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I67" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J67" s="3" t="n">
+      <c r="G67" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H67" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2896,22 +2491,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E68" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H68" s="3" t="n">
+      <c r="E68" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F68" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I68" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J68" s="3" t="n">
+      <c r="G68" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H68" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2932,22 +2521,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E69" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F69" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H69" s="3" t="n">
+      <c r="F69" s="4" t="n">
         <v>47508.2</v>
       </c>
-      <c r="I69" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J69" s="3" t="n">
+      <c r="G69" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H69" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2968,22 +2551,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E70" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H70" s="3" t="n">
+      <c r="E70" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F70" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="I70" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J70" s="3" t="n">
+      <c r="G70" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H70" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -3004,22 +2581,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E71" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H71" s="3" t="n">
+      <c r="E71" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F71" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I71" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J71" s="3" t="n">
+      <c r="G71" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H71" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -3040,22 +2611,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="E72" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="F72" s="3" t="n">
+      <c r="F72" s="4" t="n">
+        <v>41901.64</v>
+      </c>
+      <c r="G72" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G72" s="3" t="n">
-        <v>83803.28</v>
-      </c>
-      <c r="H72" s="3" t="n">
-        <v>41901.64</v>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>69836.07000000001</v>
-      </c>
-      <c r="J72" s="3" t="n">
+      <c r="H72" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -3076,22 +2641,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E73" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>81442.62</v>
-      </c>
-      <c r="H73" s="3" t="n">
+      <c r="E73" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F73" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="I73" s="3" t="n">
-        <v>67868.85000000001</v>
-      </c>
-      <c r="J73" s="3" t="n">
+      <c r="G73" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H73" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -3112,22 +2671,16 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E74" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="F74" s="3" t="n">
+      <c r="F74" s="4" t="n">
+        <v>27934.43</v>
+      </c>
+      <c r="G74" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G74" s="3" t="n">
-        <v>83803.28</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>27934.43</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>69836.07000000001</v>
-      </c>
-      <c r="J74" s="3" t="n">
+      <c r="H74" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -3148,36 +2701,40 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E75" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F75" s="3" t="n">
+      <c r="E75" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>20950.82</v>
+      </c>
+      <c r="G75" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="G75" s="3" t="n">
+      <c r="H75" s="4" t="n">
         <v>83803.28</v>
       </c>
-      <c r="H75" s="3" t="n">
-        <v>20950.82</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>69836.07000000001</v>
-      </c>
-      <c r="J75" s="3" t="n">
-        <v>83803.28</v>
-      </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E76" s="5" t="n">
+      <c r="E76" s="7" t="n">
         <v>43.37</v>
       </c>
-      <c r="H76" s="6" t="n">
+      <c r="F76" s="8" t="n">
         <v>3088868.98</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>3768420</v>
       </c>
     </row>
     <row r="79">

--- a/vse-loti/339444665/spec-339444665.xlsx
+++ b/vse-loti/339444665/spec-339444665.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.####"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -60,13 +62,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -488,26 +495,2252 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>27147.54</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>33934.43</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>101803.28</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>13573.77</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>6786.89</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>33934.43</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>83803.28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>54295.08</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>34918.03</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>83803.28</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>33934.43</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>10180.33</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>16967.21</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ТРУБА 57Х6 СТ20 ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>13573.77</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>13573.77</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>13573.77</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>33934.43</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>33934.43</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>83803.28</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>33934.43</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>101803.28</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>33934.43</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>33934.43</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ТРУБА 325Х8 17Г1СУ ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>75737.7</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>75737.7</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>90885.25</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ТРУБА 273Х8 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>83803.28</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ТРУБА 530Х9 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>44262.3</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>88524.59</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>106229.51</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ТРУБА 630Х9 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>56065.57</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>93442.62</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>112131.15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ТРУБА 325Х8 17Г1СУ ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>113606.56</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>75737.7</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>90885.25</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ТРУБА 530Х9 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>177049.18</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>88524.59</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>106229.51</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ТРУБА 630Х9 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>179409.84</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>93442.62</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>112131.15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>13573.77</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>10180.33</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ТРУБА 219Х6 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>6983.61</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>83803.28</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>33934.43</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>10180.33</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>10180.33</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>13573.77</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>33934.43</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>33934.43</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>47508.2</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>20360.66</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>33934.43</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>41901.64</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>83803.28</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>33934.43</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>81442.62</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ТРУБА 273Х8 СТ20 ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>27934.43</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>83803.28</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ТРУБА 219Х6 СТ20 ТИП1 К52 ГОСТ20295</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>20950.82</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>83803.28</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="E76" s="7" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>3088868.98</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F77" s="8" t="n">
         <v>3768420</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Источник: preview.txt</t>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Источник: Приложение №4. Сведения о НМЦ.xlsx</t>
         </is>
       </c>
     </row>

--- a/vse-loti/339444665/spec-339444665.xlsx
+++ b/vse-loti/339444665/spec-339444665.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -460,35 +460,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Наименование позиции (⌀ + s, если указано)</t>
+          <t>Наименование позиции</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>D×s, мм</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Кол-во (исх.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -503,24 +508,29 @@
           <t>ТРУБА 108Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>108×4</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="G2" s="4" t="n">
         <v>27147.54</v>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H2" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -533,24 +543,29 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F3" s="4" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>108×5</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H3" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -563,24 +578,29 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F4" s="4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>76×4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G4" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H4" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -593,24 +613,29 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F5" s="4" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H5" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -623,24 +648,29 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F6" s="4" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>89×5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H6" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -653,24 +683,29 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F7" s="4" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>159×6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H7" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -683,24 +718,29 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F8" s="4" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>108×5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H8" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I8" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -713,24 +753,29 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F9" s="4" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>76×4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H9" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -743,24 +788,29 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F10" s="4" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H10" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -773,24 +823,29 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F11" s="4" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>89×5</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H11" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -803,24 +858,29 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F12" s="4" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>159×6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G12" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H12" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I12" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -833,24 +893,29 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>108×5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H13" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -863,24 +928,29 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>159×6</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>101803.28</v>
       </c>
-      <c r="G14" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H14" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -893,24 +963,29 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>13573.77</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H15" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -923,24 +998,29 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>76×4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>6786.89</v>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H16" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -953,24 +1033,29 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>89×5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H17" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -983,24 +1068,29 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>67868.85000000001</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>108×5</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>67868.85000000001</v>
       </c>
       <c r="H18" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I18" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1013,24 +1103,29 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>67868.85000000001</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>159×6</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>67868.85000000001</v>
       </c>
       <c r="H19" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I19" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1043,24 +1138,29 @@
           <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>69836.07000000001</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>219×8</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
       <c r="H20" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="I20" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -1073,24 +1173,29 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F21" s="4" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G21" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G21" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H21" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I21" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1103,24 +1208,29 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F22" s="4" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>76×4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G22" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G22" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H22" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I22" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1133,24 +1243,29 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F23" s="4" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>89×5</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G23" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G23" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H23" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I23" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1163,24 +1278,29 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>67868.85000000001</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>108×5</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>67868.85000000001</v>
       </c>
       <c r="H24" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I24" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1193,24 +1313,29 @@
           <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>133×5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>54295.08</v>
       </c>
-      <c r="G25" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H25" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I25" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1223,24 +1348,29 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>67868.85000000001</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>159×6</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>67868.85000000001</v>
       </c>
       <c r="H26" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I26" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1253,24 +1383,29 @@
           <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>219×8</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>34918.03</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="I27" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -1283,24 +1418,29 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F28" s="4" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G28" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G28" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H28" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I28" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1313,24 +1453,29 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>76×4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H29" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I29" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1343,24 +1488,29 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F30" s="4" t="n">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>89×5</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G30" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G30" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H30" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I30" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1373,24 +1523,29 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>108×5</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>10180.33</v>
       </c>
-      <c r="G31" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H31" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1403,24 +1558,29 @@
           <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>133×5</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>16967.21</v>
       </c>
-      <c r="G32" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H32" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I32" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1433,24 +1593,29 @@
           <t>ТРУБА 57Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>57×6</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>13573.77</v>
       </c>
-      <c r="G33" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H33" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I33" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1463,24 +1628,29 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>76×4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>13573.77</v>
       </c>
-      <c r="G34" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H34" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I34" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1493,24 +1663,29 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>89×5</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>13573.77</v>
       </c>
-      <c r="G35" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H35" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I35" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1523,24 +1698,29 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>67868.85000000001</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>108×5</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>67868.85000000001</v>
       </c>
       <c r="H36" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I36" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1553,24 +1733,29 @@
           <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>133×5</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="G37" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H37" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I37" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1583,24 +1768,29 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>67868.85000000001</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>159×6</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>67868.85000000001</v>
       </c>
       <c r="H38" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I38" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1613,24 +1803,29 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F39" s="4" t="n">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G39" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G39" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H39" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I39" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1643,24 +1838,29 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>76×4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="G40" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H40" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I40" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1673,24 +1873,29 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>67868.85000000001</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>89×5</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G41" s="4" t="n">
         <v>67868.85000000001</v>
       </c>
       <c r="H41" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I41" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1703,24 +1908,29 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>67868.85000000001</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>108×5</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>67868.85000000001</v>
       </c>
       <c r="H42" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I42" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1733,24 +1943,29 @@
           <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>69836.07000000001</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>219×8</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
       <c r="H43" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="I43" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -1763,24 +1978,29 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F44" s="4" t="n">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G44" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G44" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H44" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I44" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1793,24 +2013,29 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>76×4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="G45" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H45" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I45" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1823,24 +2048,29 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C46" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>67868.85000000001</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>89×5</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>67868.85000000001</v>
       </c>
       <c r="H46" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I46" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1853,24 +2083,29 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>108×5</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>101803.28</v>
       </c>
-      <c r="G47" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H47" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I47" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1883,24 +2118,29 @@
           <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C48" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>67868.85000000001</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>133×5</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G48" s="4" t="n">
         <v>67868.85000000001</v>
       </c>
       <c r="H48" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I48" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1913,24 +2153,29 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>67868.85000000001</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>159×6</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G49" s="4" t="n">
         <v>67868.85000000001</v>
       </c>
       <c r="H49" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I49" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1943,24 +2188,29 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="G50" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H50" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I50" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -1973,24 +2223,29 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>76×4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="G51" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H51" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I51" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2003,24 +2258,29 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>67868.85000000001</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>89×5</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>67868.85000000001</v>
       </c>
       <c r="H52" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I52" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2033,24 +2293,29 @@
           <t>ТРУБА 325Х8 17Г1СУ ГОСТ10705</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>75737.7</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>325×8</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>75737.7</v>
       </c>
       <c r="H53" s="4" t="n">
+        <v>75737.7</v>
+      </c>
+      <c r="I53" s="4" t="n">
         <v>90885.25</v>
       </c>
     </row>
@@ -2063,24 +2328,29 @@
           <t>ТРУБА 273Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C54" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>69836.07000000001</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>273×8</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
       <c r="H54" s="4" t="n">
+        <v>69836.07000000001</v>
+      </c>
+      <c r="I54" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -2093,24 +2363,29 @@
           <t>ТРУБА 530Х9 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>530×9</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>44262.3</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>88524.59</v>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="I55" s="4" t="n">
         <v>106229.51</v>
       </c>
     </row>
@@ -2123,24 +2398,29 @@
           <t>ТРУБА 630Х9 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>630×9</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="G56" s="4" t="n">
         <v>56065.57</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="H56" s="4" t="n">
         <v>93442.62</v>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="I56" s="4" t="n">
         <v>112131.15</v>
       </c>
     </row>
@@ -2153,24 +2433,29 @@
           <t>ТРУБА 325Х8 17Г1СУ ГОСТ10705</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>325×8</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="G57" s="4" t="n">
         <v>113606.56</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>75737.7</v>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="I57" s="4" t="n">
         <v>90885.25</v>
       </c>
     </row>
@@ -2183,24 +2468,29 @@
           <t>ТРУБА 530Х9 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
         </is>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>530×9</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="G58" s="4" t="n">
         <v>177049.18</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="H58" s="4" t="n">
         <v>88524.59</v>
       </c>
-      <c r="H58" s="4" t="n">
+      <c r="I58" s="4" t="n">
         <v>106229.51</v>
       </c>
     </row>
@@ -2213,24 +2503,29 @@
           <t>ТРУБА 630Х9 СТ17Г1С ТИП3 К52 ГОСТ20295</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>630×9</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
         <v>1.92</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="G59" s="4" t="n">
         <v>179409.84</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <v>93442.62</v>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="I59" s="4" t="n">
         <v>112131.15</v>
       </c>
     </row>
@@ -2243,24 +2538,29 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>108×5</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="G60" s="4" t="n">
         <v>13573.77</v>
       </c>
-      <c r="G60" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H60" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I60" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2273,24 +2573,29 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>159×6</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="n">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="G61" s="4" t="n">
         <v>10180.33</v>
       </c>
-      <c r="G61" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H61" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I61" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2303,24 +2608,29 @@
           <t>ТРУБА 219Х6 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>219×6</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="G62" s="4" t="n">
         <v>6983.61</v>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="H62" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="I62" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -2333,24 +2643,29 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="G63" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="G63" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H63" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I63" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2363,24 +2678,29 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>76×4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="G64" s="4" t="n">
         <v>10180.33</v>
       </c>
-      <c r="G64" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H64" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I64" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2393,24 +2713,29 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>89×5</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
         <v>0.15</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="G65" s="4" t="n">
         <v>10180.33</v>
       </c>
-      <c r="G65" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H65" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I65" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2423,24 +2748,29 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="G66" s="4" t="n">
         <v>13573.77</v>
       </c>
-      <c r="G66" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H66" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I66" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2453,24 +2783,29 @@
           <t>ТРУБА 108Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>108×5</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="n">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F67" s="4" t="n">
+      <c r="G67" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="G67" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H67" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I67" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2483,24 +2818,29 @@
           <t>ТРУБА 133Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>133×5</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n">
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F68" s="4" t="n">
+      <c r="G68" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="G68" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H68" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I68" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2513,24 +2853,29 @@
           <t>ТРУБА 159Х6 СТ20 ГОСТ10705</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>159×6</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
         <v>0.7</v>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n">
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="G69" s="4" t="n">
         <v>47508.2</v>
       </c>
-      <c r="G69" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H69" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I69" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2543,24 +2888,29 @@
           <t>ТРУБА 57Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F70" s="4" t="n">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>57×4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G70" s="4" t="n">
         <v>20360.66</v>
       </c>
-      <c r="G70" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H70" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I70" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2573,24 +2923,29 @@
           <t>ТРУБА 76Х4 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>76×4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n">
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="G71" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="G71" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H71" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I71" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2603,24 +2958,29 @@
           <t>ТРУБА 219Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>219×8</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="n">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="G72" s="4" t="n">
         <v>41901.64</v>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="H72" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="H72" s="4" t="n">
+      <c r="I72" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -2633,24 +2993,29 @@
           <t>ТРУБА 89Х5 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>89×5</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="G73" s="4" t="n">
         <v>33934.43</v>
       </c>
-      <c r="G73" s="4" t="n">
-        <v>67868.85000000001</v>
-      </c>
       <c r="H73" s="4" t="n">
+        <v>67868.85000000001</v>
+      </c>
+      <c r="I73" s="4" t="n">
         <v>81442.62</v>
       </c>
     </row>
@@ -2663,24 +3028,29 @@
           <t>ТРУБА 273Х8 СТ20 ГОСТ10704</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>273×8</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
         <v>0.4</v>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="n">
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="G74" s="4" t="n">
         <v>27934.43</v>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="H74" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="H74" s="4" t="n">
+      <c r="I74" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -2693,24 +3063,29 @@
           <t>ТРУБА 219Х6 СТ20 ТИП1 К52 ГОСТ20295</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F75" s="4" t="n">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>219×6</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G75" s="4" t="n">
         <v>20950.82</v>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="H75" s="4" t="n">
         <v>69836.07000000001</v>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="I75" s="4" t="n">
         <v>83803.28</v>
       </c>
     </row>
@@ -2720,10 +3095,10 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E76" s="7" t="n">
+      <c r="F76" s="7" t="n">
         <v>43.37</v>
       </c>
-      <c r="F76" s="8" t="n">
+      <c r="G76" s="8" t="n">
         <v>3088868.98</v>
       </c>
     </row>
@@ -2733,7 +3108,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="F77" s="8" t="n">
+      <c r="G77" s="8" t="n">
         <v>3768420</v>
       </c>
     </row>
